--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-bloodglucose-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-bloodglucose-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2956" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2956" uniqueCount="568">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile is defining the Blood Glucose Observation, similar to the Observation Social History - Alcohol Use from the IPS. The blood glucose option only allows values inbetween 0 and 999 mg/dL.</t>
+    <t>This FHIR profile is defining the Blood Glucose Observation. The blood glucose option only allows values between 0 and 999 mg/dL.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}bloodglucose-range:Blood glucose must be inbetween 0 and 999 mg/dL. {value.ofType(Quantity).value &gt;= 0 and value.ofType(Quantity).value &lt;= 999}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}bloodglucose-range:Blood glucose must be between 0 and 999 mg/dL. {value.ofType(Quantity).value &gt;= 0 and value.ofType(Quantity).value &lt;= 999}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1515,6 +1515,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -8300,7 +8304,7 @@
         <v>479</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>480</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -8309,10 +8313,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8323,10 +8327,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8352,10 +8356,10 @@
         <v>476</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8406,7 +8410,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8418,7 +8422,7 @@
         <v>479</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>480</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8427,10 +8431,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8441,10 +8445,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8470,16 +8474,16 @@
         <v>182</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8507,10 +8511,10 @@
         <v>117</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8528,7 +8532,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8546,10 +8550,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>413</v>
@@ -8563,10 +8567,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8592,16 +8596,16 @@
         <v>182</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8629,10 +8633,10 @@
         <v>270</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8650,7 +8654,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8668,10 +8672,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>413</v>
@@ -8685,10 +8689,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8711,17 +8715,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8770,7 +8774,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8794,7 +8798,7 @@
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8805,10 +8809,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8834,10 +8838,10 @@
         <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8888,7 +8892,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8909,10 +8913,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8923,10 +8927,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8949,16 +8953,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9008,7 +9012,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9029,10 +9033,10 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -9043,10 +9047,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9069,16 +9073,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9128,7 +9132,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9149,10 +9153,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -9163,10 +9167,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9192,16 +9196,16 @@
         <v>460</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9238,7 +9242,7 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -9248,7 +9252,7 @@
         <v>169</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9269,10 +9273,10 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9283,10 +9287,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9401,10 +9405,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9521,10 +9525,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9643,10 +9647,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9672,13 +9676,13 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>268</v>
@@ -9730,7 +9734,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>93</v>
@@ -9748,7 +9752,7 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>275</v>
@@ -9765,10 +9769,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9791,16 +9795,16 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M64" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>344</v>
@@ -9852,7 +9856,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9870,7 +9874,7 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>347</v>
@@ -9887,10 +9891,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9916,13 +9920,13 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>398</v>
@@ -9974,7 +9978,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10009,10 +10013,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10096,7 +10100,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10131,10 +10135,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10160,10 +10164,10 @@
         <v>83</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>463</v>
@@ -10218,7 +10222,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10253,13 +10257,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>21</v>
@@ -10284,16 +10288,16 @@
         <v>460</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10342,7 +10346,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10363,10 +10367,10 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>21</v>
@@ -10377,10 +10381,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10495,10 +10499,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10615,10 +10619,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10737,10 +10741,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10766,13 +10770,13 @@
         <v>182</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>268</v>
@@ -10785,7 +10789,7 @@
         <v>21</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>21</v>
@@ -10824,7 +10828,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>93</v>
@@ -10842,7 +10846,7 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>275</v>
@@ -10859,10 +10863,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10888,13 +10892,13 @@
         <v>182</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>344</v>
@@ -10926,7 +10930,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -10944,7 +10948,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10962,7 +10966,7 @@
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>347</v>
@@ -10979,10 +10983,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11008,13 +11012,13 @@
         <v>182</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>398</v>
@@ -11066,7 +11070,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11101,10 +11105,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11188,7 +11192,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11223,10 +11227,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11252,10 +11256,10 @@
         <v>83</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>463</v>
@@ -11310,7 +11314,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
